--- a/AzentioAutomationFramework_FMS_VIJAY2/TestData/FMSTestData.xlsx
+++ b/AzentioAutomationFramework_FMS_VIJAY2/TestData/FMSTestData.xlsx
@@ -1,25 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" tabRatio="971" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" tabRatio="971" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="AllFeaturesTestExecutionInfo" sheetId="8" r:id="rId1"/>
     <sheet name="AllFeaturesTestDataInstructions" sheetId="5" r:id="rId2"/>
-    <sheet name="FMS_Login" sheetId="1" r:id="rId3"/>
-    <sheet name="FMSParam_login" sheetId="2" r:id="rId4"/>
-    <sheet name="SadsLogin" sheetId="3" r:id="rId5"/>
-    <sheet name="TestExecution" sheetId="7" r:id="rId6"/>
+    <sheet name="CSMParam_login" sheetId="10" r:id="rId3"/>
+    <sheet name="CSM_Login" sheetId="9" r:id="rId4"/>
+    <sheet name="FMSParam_login" sheetId="2" r:id="rId5"/>
+    <sheet name="FMS_Login" sheetId="1" r:id="rId6"/>
+    <sheet name="SadsLogin" sheetId="3" r:id="rId7"/>
+    <sheet name="ApplicationForFinancialFacility" sheetId="11" r:id="rId8"/>
+    <sheet name="TestExecution" sheetId="7" r:id="rId9"/>
+    <sheet name="FMS_WIFAK_ApplicationTestData" sheetId="12" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="116">
   <si>
     <t>Password</t>
   </si>
@@ -109,9 +113,6 @@
     <t>EndExecution</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Master Screen Name</t>
   </si>
   <si>
@@ -139,12 +140,6 @@
     <t>MODEL.B</t>
   </si>
   <si>
-    <t>Fms_01</t>
-  </si>
-  <si>
-    <t>Fms_01_D1</t>
-  </si>
-  <si>
     <t>UserName</t>
   </si>
   <si>
@@ -260,6 +255,126 @@
   </si>
   <si>
     <t>FMS_ParamUser12</t>
+  </si>
+  <si>
+    <t>TestCase ID</t>
+  </si>
+  <si>
+    <t>DataSet ID</t>
+  </si>
+  <si>
+    <t>ApplicationFor</t>
+  </si>
+  <si>
+    <t>New Facility</t>
+  </si>
+  <si>
+    <t>CIF NO</t>
+  </si>
+  <si>
+    <t>Facility Type</t>
+  </si>
+  <si>
+    <t>Country of Financing</t>
+  </si>
+  <si>
+    <t>Min Value</t>
+  </si>
+  <si>
+    <t>Max Value</t>
+  </si>
+  <si>
+    <t>999999999999999</t>
+  </si>
+  <si>
+    <t>AFFF_01</t>
+  </si>
+  <si>
+    <t>AFFF_01_D1</t>
+  </si>
+  <si>
+    <t>Search Code</t>
+  </si>
+  <si>
+    <t>Collateral</t>
+  </si>
+  <si>
+    <t>Collaterals defined</t>
+  </si>
+  <si>
+    <t>Application For</t>
+  </si>
+  <si>
+    <t>Facility Ref</t>
+  </si>
+  <si>
+    <t>CIF No</t>
+  </si>
+  <si>
+    <t>Facility Rating</t>
+  </si>
+  <si>
+    <t>Total value</t>
+  </si>
+  <si>
+    <t>Expire Date</t>
+  </si>
+  <si>
+    <t>Finance Amount</t>
+  </si>
+  <si>
+    <t>Down Payment %</t>
+  </si>
+  <si>
+    <t>Down Payment to Vendor %</t>
+  </si>
+  <si>
+    <t>Limit Details Item</t>
+  </si>
+  <si>
+    <t>Product Class</t>
+  </si>
+  <si>
+    <t>Margin Rate</t>
+  </si>
+  <si>
+    <t>CV Value</t>
+  </si>
+  <si>
+    <t>Charges Details Code</t>
+  </si>
+  <si>
+    <t>Document Code</t>
+  </si>
+  <si>
+    <t>Line No</t>
+  </si>
+  <si>
+    <t>Solicitor Name</t>
+  </si>
+  <si>
+    <t>Estimator Name</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Recommendation</t>
+  </si>
+  <si>
+    <t>More Comments</t>
+  </si>
+  <si>
+    <t>DS01_326257</t>
+  </si>
+  <si>
+    <t>DS01_402669</t>
+  </si>
+  <si>
+    <t>Revolving/One-Off</t>
+  </si>
+  <si>
+    <t>Revolving</t>
   </si>
 </sst>
 </file>
@@ -270,7 +385,7 @@
     <numFmt numFmtId="164" formatCode="&quot;Rs.&quot;#,##0.00;[Red]\-&quot;Rs.&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -340,8 +455,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,6 +515,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6A6A6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2B2B2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,7 +590,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
@@ -513,6 +659,43 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -852,7 +1035,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -875,28 +1058,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>35</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75">
@@ -1054,6 +1237,563 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="4.5870078740157476" bottom="4.5870078740157476" header="4.3901574803149597" footer="4.3901574803149597"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AC14"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" customWidth="1"/>
+    <col min="11" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="26.140625" customWidth="1"/>
+    <col min="18" max="18" width="17.42578125" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" customWidth="1"/>
+    <col min="21" max="21" width="11.85546875" customWidth="1"/>
+    <col min="22" max="22" width="21.5703125" customWidth="1"/>
+    <col min="23" max="23" width="19.7109375" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" customWidth="1"/>
+    <col min="25" max="25" width="15.7109375" customWidth="1"/>
+    <col min="26" max="26" width="15.5703125" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" customWidth="1"/>
+    <col min="28" max="28" width="19.28515625" customWidth="1"/>
+    <col min="29" max="29" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" ht="30">
+      <c r="A1" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="L1" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q1" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="S1" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="T1" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="U1" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="V1" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="W1" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="X1" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y1" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z1" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA1" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB1" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC1" s="44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
+      <c r="A2" s="47">
+        <v>326257</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="49"/>
+      <c r="H2" s="50">
+        <v>727</v>
+      </c>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50">
+        <v>320</v>
+      </c>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="49"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="48"/>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" s="47">
+        <v>402669</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="48"/>
+      <c r="H3" s="50">
+        <v>727</v>
+      </c>
+      <c r="I3" s="48">
+        <v>369</v>
+      </c>
+      <c r="J3" s="48">
+        <v>840</v>
+      </c>
+      <c r="K3" s="48">
+        <v>2</v>
+      </c>
+      <c r="L3" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="M3" s="48"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+    </row>
+    <row r="4" spans="1:29">
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="50"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="49"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="48"/>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="47"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="50"/>
+      <c r="U5" s="50"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="52"/>
+      <c r="Z5" s="52"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="48"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="50"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="50"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
+      <c r="V6" s="52"/>
+      <c r="W6" s="52"/>
+      <c r="X6" s="52"/>
+      <c r="Y6" s="52"/>
+      <c r="Z6" s="52"/>
+      <c r="AA6" s="49"/>
+      <c r="AB6" s="49"/>
+      <c r="AC6" s="48"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="47"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="48"/>
+      <c r="W7" s="48"/>
+      <c r="X7" s="48"/>
+      <c r="Y7" s="48"/>
+      <c r="Z7" s="48"/>
+      <c r="AA7" s="48"/>
+      <c r="AB7" s="48"/>
+      <c r="AC7" s="48"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="47"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="48"/>
+      <c r="Z8" s="48"/>
+      <c r="AA8" s="48"/>
+      <c r="AB8" s="48"/>
+      <c r="AC8" s="50"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="47"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="48"/>
+      <c r="X9" s="48"/>
+      <c r="Y9" s="48"/>
+      <c r="Z9" s="48"/>
+      <c r="AA9" s="48"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="54"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="48"/>
+      <c r="W10" s="48"/>
+      <c r="X10" s="48"/>
+      <c r="Y10" s="52"/>
+      <c r="Z10" s="52"/>
+      <c r="AA10" s="49"/>
+      <c r="AB10" s="48"/>
+      <c r="AC10" s="48"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="54"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+      <c r="V11" s="48"/>
+      <c r="W11" s="48"/>
+      <c r="X11" s="48"/>
+      <c r="Y11" s="52"/>
+      <c r="Z11" s="52"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="48"/>
+      <c r="AC11" s="48"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="54"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="48"/>
+      <c r="X12" s="48"/>
+      <c r="Y12" s="52"/>
+      <c r="Z12" s="52"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="48"/>
+      <c r="AC12" s="48"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="54"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="48"/>
+      <c r="W13" s="48"/>
+      <c r="X13" s="48"/>
+      <c r="Y13" s="52"/>
+      <c r="Z13" s="52"/>
+      <c r="AA13" s="49"/>
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="48"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="55"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="50"/>
+      <c r="T14" s="48"/>
+      <c r="U14" s="48"/>
+      <c r="V14" s="48"/>
+      <c r="W14" s="48"/>
+      <c r="X14" s="48"/>
+      <c r="Y14" s="52"/>
+      <c r="Z14" s="52"/>
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="48"/>
+      <c r="AC14" s="48"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1126,20 +1866,20 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C1" s="37" t="s">
         <v>0</v>
@@ -1153,10 +1893,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1">
         <v>123</v>
@@ -1170,7 +1910,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -1187,10 +1927,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1">
         <v>321</v>
@@ -1204,10 +1944,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1">
         <v>321</v>
@@ -1221,10 +1961,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1">
         <v>321</v>
@@ -1238,10 +1978,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1">
         <v>321</v>
@@ -1255,10 +1995,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1">
         <v>321</v>
@@ -1272,10 +2012,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" s="1">
         <v>321</v>
@@ -1289,10 +2029,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1">
         <v>321</v>
@@ -1306,10 +2046,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1">
         <v>321</v>
@@ -1323,10 +2063,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C12" s="1">
         <v>321</v>
@@ -1340,10 +2080,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1">
         <v>321</v>
@@ -1362,6 +2102,246 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9.28515625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>123</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>321</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1">
+        <v>321</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="1">
+        <v>321</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="1">
+        <v>321</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="1">
+        <v>321</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="1">
+        <v>321</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="1">
+        <v>321</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1">
+        <v>321</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="1">
+        <v>321</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="1">
+        <v>321</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="1">
+        <v>321</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="1.045275590551181" bottom="1.045275590551181" header="0.84842519685039375" footer="0.84842519685039375"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15"/>
@@ -1376,10 +2356,10 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="36" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>0</v>
@@ -1393,10 +2373,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1">
         <v>123</v>
@@ -1410,7 +2390,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -1427,10 +2407,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1">
         <v>321</v>
@@ -1444,10 +2424,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1">
         <v>321</v>
@@ -1461,10 +2441,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1">
         <v>321</v>
@@ -1478,10 +2458,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1">
         <v>321</v>
@@ -1495,10 +2475,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1">
         <v>321</v>
@@ -1512,10 +2492,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" s="1">
         <v>321</v>
@@ -1529,10 +2509,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1">
         <v>321</v>
@@ -1546,10 +2526,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1">
         <v>321</v>
@@ -1563,10 +2543,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C12" s="1">
         <v>321</v>
@@ -1580,10 +2560,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1">
         <v>321</v>
@@ -1601,7 +2581,247 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.28515625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>123</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>321</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1">
+        <v>321</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="1">
+        <v>321</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="1">
+        <v>321</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="1">
+        <v>321</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="1">
+        <v>321</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="1">
+        <v>321</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1">
+        <v>321</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="1">
+        <v>321</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="1">
+        <v>321</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="1">
+        <v>321</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="1.045275590551181" bottom="1.045275590551181" header="0.84842519685039375" footer="0.84842519685039375"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15"/>
@@ -1614,10 +2834,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C1" s="37" t="s">
         <v>0</v>
@@ -1625,7 +2845,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -1636,10 +2856,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1">
         <v>123</v>
@@ -1651,7 +2871,80 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15">
+      <c r="A1" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15">
+      <c r="A2" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="42">
+        <v>727</v>
+      </c>
+      <c r="E2" s="42">
+        <v>369</v>
+      </c>
+      <c r="F2" s="42">
+        <v>320</v>
+      </c>
+      <c r="G2" s="42">
+        <v>2</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="40" defaultRowHeight="15"/>
@@ -1704,13 +2997,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -1800,7 +3093,7 @@
       <c r="J8" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2 D4:D8">
     <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",D2)))</formula>
     </cfRule>

--- a/AzentioAutomationFramework_FMS_VIJAY2/TestData/FMSTestData.xlsx
+++ b/AzentioAutomationFramework_FMS_VIJAY2/TestData/FMSTestData.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" tabRatio="971" activeTab="9"/>
@@ -18,12 +18,12 @@
     <sheet name="TestExecution" sheetId="7" r:id="rId9"/>
     <sheet name="FMS_WIFAK_ApplicationTestData" sheetId="12" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="118">
   <si>
     <t>Password</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>Revolving</t>
+  </si>
+  <si>
+    <t>DS01_834958</t>
+  </si>
+  <si>
+    <t>MarketedBY</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1041,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1242,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -1254,27 +1260,27 @@
     <col min="7" max="7" width="12.85546875" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" customWidth="1"/>
     <col min="10" max="10" width="21.5703125" customWidth="1"/>
-    <col min="11" max="12" width="15.85546875" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="18.140625" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="17" width="26.140625" customWidth="1"/>
-    <col min="18" max="18" width="17.42578125" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" customWidth="1"/>
-    <col min="21" max="21" width="11.85546875" customWidth="1"/>
-    <col min="22" max="22" width="21.5703125" customWidth="1"/>
-    <col min="23" max="23" width="19.7109375" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" customWidth="1"/>
-    <col min="25" max="25" width="15.7109375" customWidth="1"/>
-    <col min="26" max="26" width="15.5703125" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" customWidth="1"/>
-    <col min="28" max="28" width="19.28515625" customWidth="1"/>
-    <col min="29" max="29" width="15.42578125" customWidth="1"/>
+    <col min="11" max="13" width="15.85546875" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="18.140625" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
+    <col min="18" max="18" width="26.140625" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" customWidth="1"/>
+    <col min="23" max="23" width="21.5703125" customWidth="1"/>
+    <col min="24" max="24" width="19.7109375" customWidth="1"/>
+    <col min="25" max="25" width="8.140625" customWidth="1"/>
+    <col min="26" max="26" width="15.7109375" customWidth="1"/>
+    <col min="27" max="27" width="15.5703125" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" customWidth="1"/>
+    <col min="29" max="29" width="19.28515625" customWidth="1"/>
+    <col min="30" max="30" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="30">
+    <row r="1" spans="1:30" ht="30">
       <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
@@ -1312,58 +1318,61 @@
         <v>114</v>
       </c>
       <c r="M1" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="N1" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="N1" s="46" t="s">
+      <c r="O1" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="O1" s="45" t="s">
+      <c r="P1" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="P1" s="45" t="s">
+      <c r="Q1" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="Q1" s="45" t="s">
+      <c r="R1" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="R1" s="45" t="s">
+      <c r="S1" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="S1" s="45" t="s">
+      <c r="T1" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="T1" s="45" t="s">
+      <c r="U1" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="U1" s="45" t="s">
+      <c r="V1" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="V1" s="45" t="s">
+      <c r="W1" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="W1" s="45" t="s">
+      <c r="X1" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="X1" s="45" t="s">
+      <c r="Y1" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="Y1" s="45" t="s">
+      <c r="Z1" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="Z1" s="45" t="s">
+      <c r="AA1" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="AA1" s="45" t="s">
+      <c r="AB1" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="AB1" s="45" t="s">
+      <c r="AC1" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="AC1" s="44" t="s">
+      <c r="AD1" s="44" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:30">
       <c r="A2" s="47">
         <v>326257</v>
       </c>
@@ -1387,24 +1396,25 @@
       <c r="K2" s="50"/>
       <c r="L2" s="50"/>
       <c r="M2" s="50"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="48"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="50"/>
       <c r="Q2" s="48"/>
       <c r="R2" s="48"/>
-      <c r="S2" s="50"/>
+      <c r="S2" s="48"/>
       <c r="T2" s="50"/>
       <c r="U2" s="50"/>
-      <c r="V2" s="52"/>
+      <c r="V2" s="50"/>
       <c r="W2" s="52"/>
       <c r="X2" s="52"/>
       <c r="Y2" s="52"/>
       <c r="Z2" s="52"/>
-      <c r="AA2" s="49"/>
+      <c r="AA2" s="52"/>
       <c r="AB2" s="49"/>
-      <c r="AC2" s="48"/>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="48"/>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3" s="47">
         <v>402669</v>
       </c>
@@ -1433,9 +1443,9 @@
       <c r="L3" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="M3" s="48"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="48"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="53"/>
       <c r="P3" s="48"/>
       <c r="Q3" s="48"/>
       <c r="R3" s="48"/>
@@ -1450,39 +1460,57 @@
       <c r="AA3" s="48"/>
       <c r="AB3" s="48"/>
       <c r="AC3" s="48"/>
-    </row>
-    <row r="4" spans="1:29">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
+      <c r="AD3" s="48"/>
+    </row>
+    <row r="4" spans="1:30">
+      <c r="A4" s="47">
+        <v>834958</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>116</v>
+      </c>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
       <c r="E4" s="48"/>
-      <c r="F4" s="49"/>
+      <c r="F4" s="49" t="s">
+        <v>79</v>
+      </c>
       <c r="G4" s="49"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
+      <c r="H4" s="50">
+        <v>727</v>
+      </c>
+      <c r="I4" s="48">
+        <v>369</v>
+      </c>
+      <c r="J4" s="50">
+        <v>320</v>
+      </c>
+      <c r="K4" s="48">
+        <v>2</v>
+      </c>
       <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="48"/>
+      <c r="M4" s="50">
+        <v>180456</v>
+      </c>
+      <c r="N4" s="50"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="50"/>
       <c r="Q4" s="48"/>
       <c r="R4" s="48"/>
-      <c r="S4" s="50"/>
+      <c r="S4" s="48"/>
       <c r="T4" s="50"/>
       <c r="U4" s="50"/>
-      <c r="V4" s="52"/>
+      <c r="V4" s="50"/>
       <c r="W4" s="52"/>
       <c r="X4" s="52"/>
       <c r="Y4" s="52"/>
       <c r="Z4" s="52"/>
-      <c r="AA4" s="49"/>
+      <c r="AA4" s="52"/>
       <c r="AB4" s="49"/>
-      <c r="AC4" s="48"/>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="48"/>
+    </row>
+    <row r="5" spans="1:30">
       <c r="A5" s="47"/>
       <c r="B5" s="47"/>
       <c r="C5" s="50"/>
@@ -1496,24 +1524,25 @@
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
       <c r="M5" s="50"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="48"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="51"/>
+      <c r="P5" s="50"/>
       <c r="Q5" s="48"/>
       <c r="R5" s="48"/>
-      <c r="S5" s="50"/>
+      <c r="S5" s="48"/>
       <c r="T5" s="50"/>
       <c r="U5" s="50"/>
-      <c r="V5" s="52"/>
+      <c r="V5" s="50"/>
       <c r="W5" s="52"/>
       <c r="X5" s="52"/>
       <c r="Y5" s="52"/>
       <c r="Z5" s="52"/>
-      <c r="AA5" s="49"/>
+      <c r="AA5" s="52"/>
       <c r="AB5" s="49"/>
-      <c r="AC5" s="48"/>
-    </row>
-    <row r="6" spans="1:29">
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="48"/>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6" s="47"/>
       <c r="B6" s="47"/>
       <c r="C6" s="50"/>
@@ -1527,24 +1556,25 @@
       <c r="K6" s="50"/>
       <c r="L6" s="50"/>
       <c r="M6" s="50"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="48"/>
+      <c r="N6" s="50"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="50"/>
       <c r="Q6" s="48"/>
       <c r="R6" s="48"/>
-      <c r="S6" s="50"/>
+      <c r="S6" s="48"/>
       <c r="T6" s="50"/>
       <c r="U6" s="50"/>
-      <c r="V6" s="52"/>
+      <c r="V6" s="50"/>
       <c r="W6" s="52"/>
       <c r="X6" s="52"/>
       <c r="Y6" s="52"/>
       <c r="Z6" s="52"/>
-      <c r="AA6" s="49"/>
+      <c r="AA6" s="52"/>
       <c r="AB6" s="49"/>
-      <c r="AC6" s="48"/>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AC6" s="49"/>
+      <c r="AD6" s="48"/>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7" s="47"/>
       <c r="B7" s="47"/>
       <c r="C7" s="48"/>
@@ -1558,15 +1588,15 @@
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="51"/>
       <c r="P7" s="50"/>
       <c r="Q7" s="50"/>
       <c r="R7" s="50"/>
       <c r="S7" s="50"/>
       <c r="T7" s="50"/>
       <c r="U7" s="50"/>
-      <c r="V7" s="48"/>
+      <c r="V7" s="50"/>
       <c r="W7" s="48"/>
       <c r="X7" s="48"/>
       <c r="Y7" s="48"/>
@@ -1574,8 +1604,9 @@
       <c r="AA7" s="48"/>
       <c r="AB7" s="48"/>
       <c r="AC7" s="48"/>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AD7" s="48"/>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8" s="47"/>
       <c r="B8" s="47"/>
       <c r="C8" s="48"/>
@@ -1589,8 +1620,8 @@
       <c r="K8" s="48"/>
       <c r="L8" s="48"/>
       <c r="M8" s="48"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="53"/>
       <c r="P8" s="48"/>
       <c r="Q8" s="48"/>
       <c r="R8" s="48"/>
@@ -1604,9 +1635,10 @@
       <c r="Z8" s="48"/>
       <c r="AA8" s="48"/>
       <c r="AB8" s="48"/>
-      <c r="AC8" s="50"/>
-    </row>
-    <row r="9" spans="1:29">
+      <c r="AC8" s="48"/>
+      <c r="AD8" s="50"/>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9" s="47"/>
       <c r="B9" s="47"/>
       <c r="C9" s="48"/>
@@ -1620,8 +1652,8 @@
       <c r="K9" s="48"/>
       <c r="L9" s="48"/>
       <c r="M9" s="48"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="53"/>
       <c r="P9" s="48"/>
       <c r="Q9" s="48"/>
       <c r="R9" s="48"/>
@@ -1636,8 +1668,9 @@
       <c r="AA9" s="48"/>
       <c r="AB9" s="48"/>
       <c r="AC9" s="48"/>
-    </row>
-    <row r="10" spans="1:29">
+      <c r="AD9" s="48"/>
+    </row>
+    <row r="10" spans="1:30">
       <c r="A10" s="54"/>
       <c r="B10" s="47"/>
       <c r="C10" s="50"/>
@@ -1651,24 +1684,25 @@
       <c r="K10" s="50"/>
       <c r="L10" s="50"/>
       <c r="M10" s="50"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="48"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="50"/>
       <c r="Q10" s="48"/>
       <c r="R10" s="48"/>
-      <c r="S10" s="50"/>
+      <c r="S10" s="48"/>
       <c r="T10" s="50"/>
       <c r="U10" s="50"/>
-      <c r="V10" s="48"/>
+      <c r="V10" s="50"/>
       <c r="W10" s="48"/>
       <c r="X10" s="48"/>
-      <c r="Y10" s="52"/>
+      <c r="Y10" s="48"/>
       <c r="Z10" s="52"/>
-      <c r="AA10" s="49"/>
-      <c r="AB10" s="48"/>
+      <c r="AA10" s="52"/>
+      <c r="AB10" s="49"/>
       <c r="AC10" s="48"/>
-    </row>
-    <row r="11" spans="1:29">
+      <c r="AD10" s="48"/>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11" s="54"/>
       <c r="B11" s="47"/>
       <c r="C11" s="48"/>
@@ -1682,8 +1716,8 @@
       <c r="K11" s="48"/>
       <c r="L11" s="48"/>
       <c r="M11" s="48"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="51"/>
       <c r="P11" s="48"/>
       <c r="Q11" s="48"/>
       <c r="R11" s="48"/>
@@ -1693,13 +1727,14 @@
       <c r="V11" s="48"/>
       <c r="W11" s="48"/>
       <c r="X11" s="48"/>
-      <c r="Y11" s="52"/>
+      <c r="Y11" s="48"/>
       <c r="Z11" s="52"/>
-      <c r="AA11" s="49"/>
-      <c r="AB11" s="48"/>
+      <c r="AA11" s="52"/>
+      <c r="AB11" s="49"/>
       <c r="AC11" s="48"/>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11" s="48"/>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12" s="54"/>
       <c r="B12" s="55"/>
       <c r="C12" s="50"/>
@@ -1713,24 +1748,25 @@
       <c r="K12" s="50"/>
       <c r="L12" s="50"/>
       <c r="M12" s="50"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="48"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="50"/>
       <c r="Q12" s="48"/>
       <c r="R12" s="48"/>
-      <c r="S12" s="50"/>
+      <c r="S12" s="48"/>
       <c r="T12" s="50"/>
       <c r="U12" s="50"/>
-      <c r="V12" s="48"/>
+      <c r="V12" s="50"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
-      <c r="Y12" s="52"/>
+      <c r="Y12" s="48"/>
       <c r="Z12" s="52"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="48"/>
+      <c r="AA12" s="52"/>
+      <c r="AB12" s="49"/>
       <c r="AC12" s="48"/>
-    </row>
-    <row r="13" spans="1:29">
+      <c r="AD12" s="48"/>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13" s="54"/>
       <c r="B13" s="55"/>
       <c r="C13" s="48"/>
@@ -1744,8 +1780,8 @@
       <c r="K13" s="50"/>
       <c r="L13" s="50"/>
       <c r="M13" s="50"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="48"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="51"/>
       <c r="P13" s="48"/>
       <c r="Q13" s="48"/>
       <c r="R13" s="48"/>
@@ -1755,13 +1791,14 @@
       <c r="V13" s="48"/>
       <c r="W13" s="48"/>
       <c r="X13" s="48"/>
-      <c r="Y13" s="52"/>
+      <c r="Y13" s="48"/>
       <c r="Z13" s="52"/>
-      <c r="AA13" s="49"/>
-      <c r="AB13" s="48"/>
+      <c r="AA13" s="52"/>
+      <c r="AB13" s="49"/>
       <c r="AC13" s="48"/>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD13" s="48"/>
+    </row>
+    <row r="14" spans="1:30">
       <c r="A14" s="55"/>
       <c r="B14" s="55"/>
       <c r="C14" s="48"/>
@@ -1775,22 +1812,23 @@
       <c r="K14" s="50"/>
       <c r="L14" s="50"/>
       <c r="M14" s="50"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="48"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="51"/>
       <c r="P14" s="48"/>
       <c r="Q14" s="48"/>
       <c r="R14" s="48"/>
-      <c r="S14" s="50"/>
-      <c r="T14" s="48"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="50"/>
       <c r="U14" s="48"/>
       <c r="V14" s="48"/>
       <c r="W14" s="48"/>
       <c r="X14" s="48"/>
-      <c r="Y14" s="52"/>
+      <c r="Y14" s="48"/>
       <c r="Z14" s="52"/>
-      <c r="AA14" s="49"/>
-      <c r="AB14" s="48"/>
+      <c r="AA14" s="52"/>
+      <c r="AB14" s="49"/>
       <c r="AC14" s="48"/>
+      <c r="AD14" s="48"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AzentioAutomationFramework_FMS_VIJAY2/TestData/FMSTestData.xlsx
+++ b/AzentioAutomationFramework_FMS_VIJAY2/TestData/FMSTestData.xlsx
@@ -1041,7 +1041,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1389,7 +1389,9 @@
       <c r="H2" s="50">
         <v>727</v>
       </c>
-      <c r="I2" s="50"/>
+      <c r="I2" s="50">
+        <v>369</v>
+      </c>
       <c r="J2" s="50">
         <v>320</v>
       </c>
